--- a/outputs/evaluation/requirement/validation/gemini-3-5-flash-lite/CF_M06/third/CF_M06_req_eval.xlsx
+++ b/outputs/evaluation/requirement/validation/gemini-3-5-flash-lite/CF_M06/third/CF_M06_req_eval.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -546,6 +551,9 @@
         <v>0.9671999999999999</v>
       </c>
       <c r="D13" t="n">
+        <v>0.9833</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.9566</v>
       </c>
     </row>
@@ -755,10 +763,6 @@
           <t>The system shall allow the partner to create a new location for a client.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>FR</t>
@@ -772,10 +776,6 @@
           <t>Partners to create a new location for a client.</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -806,10 +806,6 @@
           <t>The system shall allow the partner to change the application language.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>FR</t>
@@ -823,10 +819,6 @@
           <t>Partners to change the language of the application.</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -857,10 +849,6 @@
           <t>The system shall allow the partner to consult the list of their clients.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>FR</t>
@@ -874,10 +862,6 @@
           <t>Partners to consult the list of their clients.</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -908,10 +892,6 @@
           <t>The system shall allow the partner to consult the current status of the different players of their clients.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>FR</t>
@@ -925,10 +905,6 @@
           <t>Partners to consult the current status of the different players of their clients.</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -959,10 +935,6 @@
           <t>The system shall allow the partner to change their password.</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>FR</t>
@@ -976,10 +948,6 @@
           <t>Partners to change their password.</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1010,10 +978,6 @@
           <t>The system shall allow the partner to visualize general information of a player.</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1027,10 +991,6 @@
           <t>Partners to view general information of a player.</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1061,10 +1021,6 @@
           <t>The system shall allow the partner to visualize advanced information of a player.</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1078,10 +1034,6 @@
           <t>Partners to view advanced information of a player.</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1112,10 +1064,6 @@
           <t>The system shall allow the partner to consult the list of locations of a previously selected client.</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1129,10 +1077,6 @@
           <t>Partners to consult the list of locations of a previously selected client.</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1163,10 +1107,6 @@
           <t>The system shall allow the partner to customize push notifications.</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1180,10 +1120,6 @@
           <t>Partners to customize push notifications.</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1214,10 +1150,6 @@
           <t>The system shall allow the partner to consult the log history of a player.</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1231,10 +1163,6 @@
           <t>Partners to consult the log history of a player.</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1265,10 +1193,6 @@
           <t>The system shall allow the partner to edit the configuration of a player.</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1282,10 +1206,6 @@
           <t>Partners to edit the configuration of a player.</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1316,10 +1236,6 @@
           <t>The system shall allow the partner to receive push notifications.</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1333,10 +1249,6 @@
           <t>Partners to receive push notifications.</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1367,10 +1279,6 @@
           <t>The system shall allow the partner to perform different actions on a player in real time.</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1384,10 +1292,6 @@
           <t>Partners to perform different actions on a player in real time.</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1418,10 +1322,6 @@
           <t>The system shall allow the partner to edit their profile information.</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1435,10 +1335,6 @@
           <t>Partners to edit their profile information.</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1469,10 +1365,6 @@
           <t>The system shall allow the partner to visualize the uptime of a player.</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1486,10 +1378,6 @@
           <t>Partners to view the uptime of a player.</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1520,10 +1408,6 @@
           <t>The system shall allow the partner to consult a list of received push notifications.</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1537,10 +1421,6 @@
           <t>Partners to consult a list of received push notifications.</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1571,14 +1451,11 @@
           <t>Buttons for different actions shall be displayed on a player's screen: reboot players, shutdown, force synchronization, and restart playback.</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>R_17</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1592,14 +1469,11 @@
           <t>On the player screen, buttons are displayed for different actions: restart players, turn off, force synchronization, and restart playback.</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>CF_M06_R17</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1630,14 +1504,11 @@
           <t>Read and unread notifications shall be differentiated.</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>R_36</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1651,14 +1522,11 @@
           <t>Read and unread notifications are differentiated.</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>CF_M06_R36</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1689,14 +1557,11 @@
           <t>A list of locations with their respective players shall be displayed.</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>R_05</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1710,14 +1575,11 @@
           <t>A list of locations with their respective players is displayed.</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>CF_M06_R05</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1748,14 +1610,11 @@
           <t>In the list of a client's locations, information on the current status and the last connection shall be displayed for each player.</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>R_15</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1769,14 +1628,11 @@
           <t>In the list of locations of a client, each player displays information about its current status and last connection.</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>CF_M06_R15</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1807,14 +1663,11 @@
           <t>Each log shall contain information about the content that has been played.</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>R_26</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1828,14 +1681,11 @@
           <t>Each log contains information about the content that has been played.</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>CF_M06_R26</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1866,14 +1716,11 @@
           <t>The user shall be able to modify profile information such as name, profile picture, etc.</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>R_40</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1887,14 +1734,11 @@
           <t>The user can modify their profile information, such as name, profile picture, etc.</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>CF_M06_R40</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1925,14 +1769,11 @@
           <t>In the NOTIFICATIONS tab, a list of received notifications ordered chronologically shall be displayed.</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>R_36</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1946,14 +1787,11 @@
           <t>In the NOTIFICATIONS tab, a list of received notifications is displayed, sorted chronologically.</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>CF_M06_R36</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1984,14 +1822,11 @@
           <t>The user shall be able to filter the list by different criteria and also sort it.</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2005,14 +1840,11 @@
           <t>The user can filter the list by different criteria and sort the list.</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>CF_M06_R01</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2043,14 +1875,11 @@
           <t>The user shall be able to filter the list by different criteria.</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>R_05</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2064,14 +1893,11 @@
           <t>The user can filter the list by different criteria.</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>CF_M06_R05</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2102,14 +1928,11 @@
           <t>Each category shall contain information and buttons to perform changes.</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>R_21</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2123,14 +1946,11 @@
           <t>Each category contains information and buttons to make changes.</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>CF_M06_R21</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2161,10 +1981,6 @@
           <t>The system shall allow the partner to initiate the registration process of a player by scanning the QR code displayed on the screen.</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>FR</t>
@@ -2178,10 +1994,6 @@
           <t>Partners to initiate the player registration process by scanning the QR code displayed on the screen.</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2212,14 +2024,11 @@
           <t>The user shall be able to select a player and access the player management view.</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>R_05</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2233,14 +2042,11 @@
           <t>The user can select a player and access the player management view.</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>CF_M06_R05</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2271,14 +2077,11 @@
           <t>A form shall be displayed to create a new location.</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>R_09</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2292,14 +2095,11 @@
           <t>A form is displayed to create a new location.</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>CF_M06_R09</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2330,14 +2130,11 @@
           <t>The user shall be able to modify their password.</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>R_42</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2351,14 +2148,11 @@
           <t>The user can modify their password.</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>CF_M06_R42</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2389,14 +2183,11 @@
           <t>The Google Maps API shall be used to facilitate address search, thereby making it easier to fill out form fields.</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>R_09</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2410,14 +2201,11 @@
           <t>The Google Maps API is used to facilitate address search, making it easier to fill out form fields.</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>CF_M06_R09</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2448,14 +2236,11 @@
           <t>The user shall be able to select a client and consult the list of locations.</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2469,14 +2254,11 @@
           <t>The user can select a client and consult the list of locations.</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>CF_M06_R01</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2507,14 +2289,11 @@
           <t>The user shall be able to choose between: Catalan, Spanish, English, French, Italian, Portuguese, and German.</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>R_46</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2528,14 +2307,11 @@
           <t>The user can choose between: Catalan, Spanish, English, French, Italian, Portuguese, and German.</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>CF_M06_R46</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2566,14 +2342,11 @@
           <t>In the PLAYLOGS tab of a player screen, a list with playback logs shall be displayed.</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>R_26</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2587,14 +2360,11 @@
           <t>In the PLAYLOGS tab of a player screen, a list with playback logs is displayed.</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>CF_M06_R26</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2625,14 +2395,11 @@
           <t>A list of clients with basic data shall be displayed.</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2646,14 +2413,11 @@
           <t>A list of clients with basic data is displayed.</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>CF_M06_R01</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2684,14 +2448,11 @@
           <t>In the UPTIME tab of a player screen, a calendar shall be displayed showing the uptime of each day by hours.</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>R_24</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2705,14 +2466,11 @@
           <t>In the UPTIME tab of a player screen, a calendar is displayed showing the uptime of each day by hours.</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>CF_M06_R24</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2743,14 +2501,11 @@
           <t>If the user clicks on a notification, it shall lead them to the corresponding player screen.</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>R_36</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2764,14 +2519,11 @@
           <t>If the user clicks on a notification, it takes them to the corresponding player screen.</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>CF_M06_R36</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2802,14 +2554,11 @@
           <t>The requirement will be understood as complete when the feedback from test users is good.</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>R_48</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2824,14 +2573,11 @@
 test is good.</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>CF_M06_R48</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2862,14 +2608,11 @@
           <t>In the INFO tab of a player screen, inside the general box, there shall be a button to edit the configuration.</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>R_30</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2883,14 +2626,11 @@
           <t>In the INFO tab of a player screen, there is a button in the general 'box' to edit the configuration.</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>CF_M06_R30</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2921,14 +2661,11 @@
           <t>The user shall be able to set the types of notifications they want to receive in 3 levels (general, per client, and per player).</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>R_34</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2942,14 +2679,11 @@
           <t>The user can set the types of notifications they want to receive at 3 levels (general, per client, and per player).</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>CF_M06_R34</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2980,14 +2714,11 @@
           <t>In the INFO tab of a player screen, boxes of different categories shall be displayed: general, configuration, preview, and storage.</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>R_19</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -3001,14 +2732,11 @@
           <t>In the INFO tab of a player screen, 'boxes' of different categories are displayed: general, configuration, preview, and storage.</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>CF_M06_R19</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3039,14 +2767,11 @@
           <t>In the ADVANCED tab of a player screen, boxes of different categories shall be displayed: actions, screen and orientation, audio, and synchronization.</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>R_21</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -3060,14 +2785,11 @@
           <t>In the ADVANCED tab of a player screen, 'boxes' of different categories are displayed: actions, screen and orientation, audio, and synchronization.</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>CF_M06_R21</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3103,9 +2825,6 @@
           <t>C_01</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>QR</t>
@@ -3129,8 +2848,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3161,14 +2878,11 @@
           <t>If the user has notification permissions enabled, they shall receive push notifications on their device in case of incidents.</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>R_32</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -3182,14 +2896,11 @@
           <t>If the user has notification permissions enabled, they will receive push notifications on their device in case of incidents.</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>CF_M06_R32</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3220,14 +2931,11 @@
           <t>If the QR code has been scanned correctly and is valid, the system shall navigate to the subsequent screens to select the client and location.</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>R_12</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -3241,14 +2949,11 @@
           <t>If the QR code is scanned correctly and is valid, the system navigates to the subsequent screens to select the client and location.</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>CF_M06_R12</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3279,14 +2984,11 @@
           <t>The requirement will be understood as complete if the application is available in the languages specified above.</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>R_56</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -3301,14 +3003,11 @@
 in the languages specified.</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>CF_M06_R56</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3339,14 +3038,11 @@
           <t>The requirement will be understood as complete if communications between the server and the application use the minimum information possible and are authenticated.</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>R_52</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -3360,14 +3056,11 @@
           <t>The requirement will be understood as complete if the communications between the server and the application use the minimum possible and authenticated information.</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>CF_M06_R52</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3398,14 +3091,11 @@
           <t>The requirement will be understood as complete if the service is continuously available.</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>R_50</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -3419,14 +3109,11 @@
           <t>The requirement will be understood as complete if the service is available continuously.</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>CF_M06_R50</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3457,14 +3144,11 @@
           <t>The user must confirm the current password in order to change it.</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>R_42</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -3478,14 +3162,11 @@
           <t>The user must confirm their current password to be able to change it.</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>CF_M06_R42</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3516,14 +3197,11 @@
           <t>The requirement will be understood as complete if the application follows the company's image.</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>R_58</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -3538,14 +3216,11 @@
 company image.</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>CF_M06_R58</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3576,14 +3251,11 @@
           <t>The password must have a minimum of 8 characters, at least one uppercase letter, at least one number, and one special character.</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>R_42</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -3597,14 +3269,11 @@
           <t>The password must have a minimum of 8 characters, at least one uppercase letter, at least one number, and one special character.</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>CF_M06_R42</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3640,9 +3309,6 @@
           <t>C_05</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
           <t>QR</t>
@@ -3666,8 +3332,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3703,9 +3367,6 @@
           <t>C_02</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>QR</t>
@@ -3729,8 +3390,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3766,9 +3425,6 @@
           <t>C_06</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>QR</t>
@@ -3792,8 +3448,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3829,9 +3483,6 @@
           <t>C_04</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>Constraint</t>
@@ -3845,9 +3496,6 @@
           <t>The application must be available for mobile devices with iOS and Android systems.</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr">
         <is>
           <t>Classification Change</t>
@@ -3888,9 +3536,6 @@
           <t>C_03</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>QR</t>
@@ -3914,8 +3559,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3946,14 +3589,11 @@
           <t>Once selected, the user only has to choose the player configuration.</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>R_12</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -3967,14 +3607,11 @@
           <t>Once selected, the user only has to choose the player configuration.</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>CF_M06_R12</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4005,14 +3642,11 @@
           <t>The requirement will be understood as complete if the application is available for both systems and works correctly.</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>R_54</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -4026,14 +3660,11 @@
           <t>The requirement will be understood as complete if the application is available for both systems and works correctly.</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>CF_M06_R54</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4064,14 +3695,11 @@
           <t>Logs can be received in real time via sockets.</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>R_26</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -4085,14 +3713,11 @@
           <t>Logs can be received in real time via sockets.</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>CF_M06_R26</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
